--- a/data/trans_dic/P1422-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P1422-Habitat-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,94</t>
+          <t>0,43; 2,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,79</t>
+          <t>0,4; 1,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,76</t>
+          <t>1,06; 2,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,36</t>
+          <t>0,15; 1,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,22</t>
+          <t>0,0; 1,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,84</t>
+          <t>0,66; 1,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,36</t>
+          <t>0,44; 1,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,15</t>
+          <t>0,29; 1,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,09</t>
+          <t>0,99; 2,04</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,82</t>
+          <t>0,5; 1,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,88</t>
+          <t>0,09; 0,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,08</t>
+          <t>0,82; 2,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,49</t>
+          <t>0,31; 1,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,73</t>
+          <t>0,32; 1,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,74</t>
+          <t>0,72; 1,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,37</t>
+          <t>0,51; 1,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,03</t>
+          <t>0,26; 0,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,59</t>
+          <t>0,89; 1,72</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,31</t>
+          <t>0,38; 2,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,48</t>
+          <t>0,14; 1,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,09</t>
+          <t>0,66; 2,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,46</t>
+          <t>0,14; 1,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,86</t>
+          <t>0,0; 0,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,2</t>
+          <t>0,31; 1,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,46</t>
+          <t>0,39; 1,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,89</t>
+          <t>0,14; 1,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,38</t>
+          <t>0,58; 1,45</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,83</t>
+          <t>0,43; 2,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,5</t>
+          <t>0,39; 1,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,51</t>
+          <t>0,46; 1,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,6</t>
+          <t>0,39; 1,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,78</t>
+          <t>0,34; 1,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,5</t>
+          <t>0,71; 1,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 1,48</t>
+          <t>0,55; 1,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,34</t>
+          <t>0,47; 1,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,3</t>
+          <t>0,71; 1,42</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,42</t>
+          <t>0,65; 1,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 0,94</t>
+          <t>0,41; 0,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,57</t>
+          <t>0,96; 1,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,06</t>
+          <t>0,46; 1,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,9</t>
+          <t>0,35; 0,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 1,22</t>
+          <t>0,81; 1,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,09</t>
+          <t>0,64; 1,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 0,84</t>
+          <t>0,43; 0,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,31</t>
+          <t>0,94; 1,36</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11218</t>
+          <t>12102</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7853</t>
+          <t>8139</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19071</t>
+          <t>20241</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3036; 13618</t>
+          <t>3050; 14474</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2733; 12083</t>
+          <t>2726; 11931</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6647; 17536</t>
+          <t>7344; 20444</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1056; 9450</t>
+          <t>1058; 10413</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 8231</t>
+          <t>0; 6946</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4905; 12419</t>
+          <t>4800; 13395</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6018; 19047</t>
+          <t>6112; 19731</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3819; 15522</t>
+          <t>3912; 16102</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13610; 27340</t>
+          <t>14095; 28973</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13782</t>
+          <t>14490</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10529</t>
+          <t>11781</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>24311</t>
+          <t>26271</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5086; 18565</t>
+          <t>5089; 18828</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>880; 8967</t>
+          <t>879; 8274</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6933; 24801</t>
+          <t>8558; 22278</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3178; 15298</t>
+          <t>3221; 15213</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4231; 18008</t>
+          <t>3332; 17574</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6564; 16683</t>
+          <t>7688; 18806</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10548; 28043</t>
+          <t>10517; 27616</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5457; 21228</t>
+          <t>5454; 19982</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14787; 34219</t>
+          <t>18866; 36513</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8272</t>
+          <t>9897</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5476</t>
+          <t>5834</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13748</t>
+          <t>15730</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2819; 17496</t>
+          <t>2905; 18195</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1125; 11267</t>
+          <t>1093; 12704</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3835; 14646</t>
+          <t>5252; 17730</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1101; 11364</t>
+          <t>1109; 11575</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6758</t>
+          <t>0; 7166</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2181; 11171</t>
+          <t>2506; 11441</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5707; 22470</t>
+          <t>6057; 23075</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1986; 13717</t>
+          <t>2161; 15514</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7901; 22559</t>
+          <t>9274; 23350</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>8349</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10940</t>
+          <t>12908</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>19272</t>
+          <t>21257</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3989; 17299</t>
+          <t>4069; 19118</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3669; 14052</t>
+          <t>3627; 13741</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4137; 13961</t>
+          <t>4559; 14277</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4120; 16883</t>
+          <t>4151; 17286</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3813; 18545</t>
+          <t>3528; 17319</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6644; 16406</t>
+          <t>7985; 19677</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10787; 29505</t>
+          <t>11093; 28972</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9192; 26574</t>
+          <t>9321; 25677</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12757; 26277</t>
+          <t>14974; 29970</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41606</t>
+          <t>44838</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34797</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>76403</t>
+          <t>83499</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>23652; 48721</t>
+          <t>22359; 48363</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>13945; 32006</t>
+          <t>13997; 32775</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30356; 54428</t>
+          <t>33968; 57277</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16597; 37842</t>
+          <t>16530; 37599</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>12769; 31761</t>
+          <t>12309; 33118</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25426; 44643</t>
+          <t>30323; 50455</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>44325; 76054</t>
+          <t>44556; 75941</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>31121; 58608</t>
+          <t>29670; 58871</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>60011; 93365</t>
+          <t>68425; 98810</t>
         </is>
       </c>
     </row>
